--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.35050356487986</v>
+        <v>8.019456829292977</v>
       </c>
       <c r="D2" t="n">
-        <v>49.76374041025495</v>
+        <v>8.086607816666429</v>
       </c>
       <c r="E2" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F2" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51291140842163</v>
+        <v>3.333348103868516</v>
       </c>
       <c r="D3" t="n">
-        <v>20.87146635039833</v>
+        <v>3.391613281939728</v>
       </c>
       <c r="E3" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F3" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.38172677372528</v>
+        <v>2.174530600730359</v>
       </c>
       <c r="D4" t="n">
-        <v>13.7785579711031</v>
+        <v>2.239015670304254</v>
       </c>
       <c r="E4" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F4" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.21474211078345</v>
+        <v>2.472395593002311</v>
       </c>
       <c r="D5" t="n">
-        <v>15.11333831889473</v>
+        <v>2.455917476820394</v>
       </c>
       <c r="E5" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F5" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.10872208104619</v>
+        <v>3.105167338170006</v>
       </c>
       <c r="D6" t="n">
-        <v>19.2797402764699</v>
+        <v>3.132957794926359</v>
       </c>
       <c r="E6" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F6" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.61140486891749</v>
+        <v>4.161853291199091</v>
       </c>
       <c r="D7" t="n">
-        <v>25.25906700443158</v>
+        <v>4.104598388220132</v>
       </c>
       <c r="E7" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F7" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.7017878991102</v>
+        <v>4.014040533605407</v>
       </c>
       <c r="D8" t="n">
-        <v>23.47110557481385</v>
+        <v>3.814054655907252</v>
       </c>
       <c r="E8" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F8" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.83838414512136</v>
+        <v>4.686237423582221</v>
       </c>
       <c r="D9" t="n">
-        <v>19.56660238571319</v>
+        <v>3.179572887678393</v>
       </c>
       <c r="E9" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F9" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.98099705455438</v>
+        <v>1.946912021365087</v>
       </c>
       <c r="D10" t="n">
-        <v>6.645219822989653</v>
+        <v>1.079848221235819</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F10" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.10624542898255</v>
+        <v>4.242264882209664</v>
       </c>
       <c r="D11" t="n">
-        <v>21.20915998504208</v>
+        <v>3.446488497569339</v>
       </c>
       <c r="E11" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F11" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.28776647687947</v>
+        <v>2.321762052492914</v>
       </c>
       <c r="D12" t="n">
-        <v>18.39152036221244</v>
+        <v>2.988622058859521</v>
       </c>
       <c r="E12" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F12" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.35532384852893</v>
+        <v>1.845240125385952</v>
       </c>
       <c r="D13" t="n">
-        <v>11.2322389177226</v>
+        <v>1.825238824129923</v>
       </c>
       <c r="E13" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F13" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.99048708730116</v>
+        <v>1.785954151686439</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75763510655433</v>
+        <v>1.748115704815078</v>
       </c>
       <c r="E14" t="n">
-        <v>10.15637159975433</v>
+        <v>1.650410384960079</v>
       </c>
       <c r="F14" t="n">
-        <v>10.12484367368707</v>
+        <v>1.645287096974148</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
